--- a/stress_tensors/rock_strength_metrics.xlsx
+++ b/stress_tensors/rock_strength_metrics.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Goodness-of-Fit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equation Fit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angle RMSE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top RMSE Points" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -586,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,11 +616,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R² (poly fit)</t>
+          <t>Rows</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.879</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -629,12 +631,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Poly fit (first 10)</t>
+          <t>sigma0 (MPa)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[10.37168666, 10.35365821, 10.334919, 10.31551897, 10.29550627, 10.27492719, 10.25382623, 10.23224606, 10.21022754, 10.18780969]</t>
+          <t>10.3013 ± 0.1127</t>
         </is>
       </c>
     </row>
@@ -646,61 +648,1222 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>95% CI (first 10)</t>
+          <t>sigma90 (MPa)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'lower': [9.92175716, 9.93566258, 9.92795692, 9.90313656, 9.86676581, 9.82390479, 9.77837151, 9.73274738, 9.68866453, 9.64710031], 'upper': [10.82161617, 10.77165384, 10.74188107, 10.72790139, 10.72424673, 10.7259496, 10.72928096, 10.73174474, 10.73179054, 10.72851907]}</t>
+          <t>7.0528 ± 0.4149</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Psammatic Schist</t>
+          <t>Augen Gneiss</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R² (poly fit)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.95</v>
+          <t>eta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.3872 ± 0.1945</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Psammatic Schist</t>
+          <t>Augen Gneiss</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Poly fit (first 10)</t>
+          <t>xi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[9.52909993, 9.46509482, 9.40249921, 9.34124577, 9.28126818, 9.22250111, 9.16488025, 9.10834227, 9.05282485, 8.9982667]</t>
+          <t>0.5471 ± 0.2263</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Psammatic Schist</t>
+          <t>Augen Gneiss</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>95% CI (first 10)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'lower': [8.88322128, 8.87396977, 8.85039353, 8.8138642, 8.76652475, 8.71100732, 8.65002134, 8.58600408, 8.52093505, 8.45630059], 'upper': [10.17497857, 10.05621987, 9.95460489, 9.86862735, 9.79601162, 9.73399491, 9.67973915, 9.63068045, 9.58471466, 9.5402328]}</t>
+          <t>trough center (deg)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>61.58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8707</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RMSE (MPa)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.604</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>χ²red</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.956</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sigma0 (MPa)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>9.5175 ± 0.4348</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sigma90 (MPa)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6.8166 ± 0.7080</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>eta</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.9689 ± 0.3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>xi</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.5802 ± 0.1692</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>trough center (deg)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>62.73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8452</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RMSE (MPa)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.637</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>χ²red</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.567</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rock Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Angle (deg)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mean Residual</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Angle RMSE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Angle SSE %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8782</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>21.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>75</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.0375</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>27.52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>90</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1972</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7657</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>21.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>13.32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12.69%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>45</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1514</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3.73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.009299999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.6271</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8441</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23.95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>90</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1466</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6947</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>16.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>75</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4954</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6666</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>19.91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>45</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6532</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>14.34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>30</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5095</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6166</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>12.78%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>9.80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>60</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.2252</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rock Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Angle (deg)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tensile_strength_Mpa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Residual</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Squared Error</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SSE %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.0528</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.4572</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.1235</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>19.41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.433</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.0079</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>18.35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>75</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.3035</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.1265</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.269</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>11.60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.3035</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.8935</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7983</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.6076</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8424</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7097</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6.49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>75</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.3035</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.8135</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6.05%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.6076</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.7976</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6361</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5.81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10.3013</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4.72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.3013</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6087</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Augen Gneiss</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>45</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.2681</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.6081</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9.063700000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.2137</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.4731</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>16.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>75</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.1946</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.1254</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.2665</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>14.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>30</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.5972</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9928</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9857</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>11.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>45</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.0523</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8077</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6524</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>7.31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9.063700000000001</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.8037</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>7.24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>90</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.8166</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7934</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6294</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>7.05%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.5175</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7925</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>7.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>45</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.0523</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.7923</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6277</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>7.03%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>90</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.8166</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.7866</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6.93%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Psammatic Schist</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>75</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.1946</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5254</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
